--- a/ALIEN-001_balance_reconciliation.xlsx
+++ b/ALIEN-001_balance_reconciliation.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -560,6 +560,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -567,6 +568,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -609,20 +611,22 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Current inventory: 0 periods present, 0 partial, ~38 periods missing (16 Account One May2023-Sep2024 + ~22 Account Two Dec2024-Oct2026). See ALIEN-001_evidence_register.csv EV-003/EV-004.</t>
+          <t>• One row per statement period (e.g., 2023-05 Account One, 2023-06 Account One, ... 2024-09 Account One, gap 2024-10/11, 2024-12 Account Two ... 2026-10 Account Two) — maximum 40 potential (17+23) on calendar-month cycle; actual depends on opening/closing dates and cycle day</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Evidence needed: EV-003 &amp; EV-004 monthly statements (PDF or CSV), EV-005 transaction exports (CSV/OFX/QFX), EV-006 opening/closing balances, EV-007 closure notice, EV-009 overdraft notices.</t>
-        </is>
-      </c>
-    </row>
+          <t>Evidence needed: EV-003 &amp; EV-004 monthly statements (PDF or CSV; up to 17 + 23 = 40 calendar-month potential), EV-005 transaction exports (CSV/OFX/QFX), EV-006 opening/closing balances, EV-007 closure notice, EV-009 overdraft notices. Actual statement count to be established from bank records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
@@ -630,6 +634,9 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="1" fitToWidth="1"/>
@@ -681,6 +688,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -766,15 +774,19 @@
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>ALL PERIODS
-MISSING</t>
+MISSING
+(up to 40 cal-mo
+potential)</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Account One
 May 2023–Sep 2024
+(up to 17 cal-mo)
 Account Two
-Dec 2024–Oct 2026</t>
+Dec 2024–Oct 2026
+(up to 23 cal-mo)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -846,10 +858,11 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Notes: 1) Preserve difference between transaction date / posting date / authorization date / settlement date. 2) Disappearing pending ≠ debit/refund/loss. 3) Transfers between Account One/Two separately accounted. 4) Each difference gets Exception ID (Gate P2). 5) Challenge Agent independently tests arithmetic per AT-03/AT-08.</t>
+          <t>Notes: 1) Preserve difference between transaction date / posting date / authorization date / settlement date. 2) Disappearing pending ≠ debit/refund/loss. 3) Transfers between Account One/Two separately accounted. 4) Each difference gets Exception ID (Gate P2). 5) Challenge Agent independently tests arithmetic per AT-03/AT-08. 6) Coverage: 40 calendar-month maximum (17+23); actual issued count per statement cycle may be lower — see verification receipt erratum.</t>
         </is>
       </c>
     </row>
